--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80489</v>
+        <v>80492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80492</v>
+        <v>80497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80497</v>
+        <v>80508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80509</v>
+        <v>80511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59598-2025 artfynd.xlsx
+++ b/artfynd/A 59598-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327499</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327432</v>
       </c>
       <c r="B3" t="n">
-        <v>80511</v>
+        <v>80515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327493</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327483</v>
       </c>
       <c r="B5" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327498</v>
       </c>
       <c r="B6" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327501</v>
       </c>
       <c r="B7" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327464</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327422</v>
       </c>
       <c r="B9" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327481</v>
       </c>
       <c r="B10" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327473</v>
       </c>
       <c r="B11" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327479</v>
       </c>
       <c r="B12" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327454</v>
       </c>
       <c r="B13" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327478</v>
       </c>
       <c r="B14" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327448</v>
       </c>
       <c r="B15" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137327470</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137327446</v>
       </c>
       <c r="B17" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137327461</v>
       </c>
       <c r="B18" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137327475</v>
       </c>
       <c r="B19" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
